--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.9640301699746</v>
+        <v>3.081654902620873</v>
       </c>
       <c r="D2" t="n">
-        <v>18.92800723924044</v>
+        <v>3.075801176376572</v>
       </c>
       <c r="E2" t="n">
-        <v>9.977370705036414</v>
+        <v>1.621322739568417</v>
       </c>
       <c r="F2" t="n">
-        <v>9.945514098582851</v>
+        <v>1.616146041019713</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.73547979645531</v>
+        <v>7.432015466923988</v>
       </c>
       <c r="D3" t="n">
-        <v>45.27043568889349</v>
+        <v>7.356445799445192</v>
       </c>
       <c r="E3" t="n">
-        <v>9.977370705036414</v>
+        <v>1.621322739568417</v>
       </c>
       <c r="F3" t="n">
-        <v>9.945514098582851</v>
+        <v>1.616146041019713</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.50377490715449</v>
+        <v>5.606863422412605</v>
       </c>
       <c r="D4" t="n">
-        <v>33.80304918731562</v>
+        <v>5.492995492938789</v>
       </c>
       <c r="E4" t="n">
-        <v>9.977370705036414</v>
+        <v>1.621322739568417</v>
       </c>
       <c r="F4" t="n">
-        <v>9.945514098582851</v>
+        <v>1.616146041019713</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.83434143662164</v>
+        <v>6.960580483451017</v>
       </c>
       <c r="D5" t="n">
-        <v>42.4719197140915</v>
+        <v>6.901686953539869</v>
       </c>
       <c r="E5" t="n">
-        <v>9.977370705036414</v>
+        <v>1.621322739568417</v>
       </c>
       <c r="F5" t="n">
-        <v>9.945514098582851</v>
+        <v>1.616146041019713</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.50645892448037</v>
+        <v>4.957299575228061</v>
       </c>
       <c r="D6" t="n">
-        <v>30.74404825856338</v>
+        <v>4.99590784201655</v>
       </c>
       <c r="E6" t="n">
-        <v>9.977370705036414</v>
+        <v>1.621322739568417</v>
       </c>
       <c r="F6" t="n">
-        <v>9.945514098582851</v>
+        <v>1.616146041019713</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.14504178305856</v>
+        <v>4.411069289747017</v>
       </c>
       <c r="D7" t="n">
-        <v>26.38904378717399</v>
+        <v>4.288219615415773</v>
       </c>
       <c r="E7" t="n">
-        <v>9.977370705036414</v>
+        <v>1.621322739568417</v>
       </c>
       <c r="F7" t="n">
-        <v>9.945514098582851</v>
+        <v>1.616146041019713</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.7811291547105</v>
+        <v>7.439433487640456</v>
       </c>
       <c r="D8" t="n">
-        <v>45.68745160043307</v>
+        <v>7.424210885070375</v>
       </c>
       <c r="E8" t="n">
-        <v>9.977370705036414</v>
+        <v>1.621322739568417</v>
       </c>
       <c r="F8" t="n">
-        <v>9.945514098582851</v>
+        <v>1.616146041019713</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.5494599431908</v>
+        <v>5.614287240768506</v>
       </c>
       <c r="D9" t="n">
-        <v>34.5287034048765</v>
+        <v>5.610914303292432</v>
       </c>
       <c r="E9" t="n">
-        <v>9.977370705036414</v>
+        <v>1.621322739568417</v>
       </c>
       <c r="F9" t="n">
-        <v>9.945514098582851</v>
+        <v>1.616146041019713</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.42629071147164</v>
+        <v>5.594272240614141</v>
       </c>
       <c r="D10" t="n">
-        <v>34.3478254955708</v>
+        <v>5.581521643030254</v>
       </c>
       <c r="E10" t="n">
-        <v>9.977370705036414</v>
+        <v>1.621322739568417</v>
       </c>
       <c r="F10" t="n">
-        <v>9.945514098582851</v>
+        <v>1.616146041019713</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>13.43056239037848</v>
+        <v>2.182466388436503</v>
       </c>
       <c r="D11" t="n">
-        <v>13.38744871852597</v>
+        <v>2.175460416760471</v>
       </c>
       <c r="E11" t="n">
-        <v>9.977370705036414</v>
+        <v>1.621322739568417</v>
       </c>
       <c r="F11" t="n">
-        <v>9.945514098582851</v>
+        <v>1.616146041019713</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>40.00895219454336</v>
+        <v>6.501454731613297</v>
       </c>
       <c r="D12" t="n">
-        <v>40.23681449392505</v>
+        <v>6.538482355262821</v>
       </c>
       <c r="E12" t="n">
-        <v>9.977370705036414</v>
+        <v>1.621322739568417</v>
       </c>
       <c r="F12" t="n">
-        <v>9.945514098582851</v>
+        <v>1.616146041019713</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>34.99108639500614</v>
+        <v>5.686051539188497</v>
       </c>
       <c r="D13" t="n">
-        <v>35.30474632550681</v>
+        <v>5.737021277894857</v>
       </c>
       <c r="E13" t="n">
-        <v>9.977370705036414</v>
+        <v>1.621322739568417</v>
       </c>
       <c r="F13" t="n">
-        <v>9.945514098582851</v>
+        <v>1.616146041019713</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>43.35777882834388</v>
+        <v>7.045639059605881</v>
       </c>
       <c r="D14" t="n">
-        <v>43.80085222367626</v>
+        <v>7.117638486347392</v>
       </c>
       <c r="E14" t="n">
-        <v>9.977370705036414</v>
+        <v>1.621322739568417</v>
       </c>
       <c r="F14" t="n">
-        <v>9.945514098582851</v>
+        <v>1.616146041019713</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>12.02615993630801</v>
+        <v>1.954250989650052</v>
       </c>
       <c r="D15" t="n">
-        <v>12.74118239354672</v>
+        <v>2.070442138951341</v>
       </c>
       <c r="E15" t="n">
-        <v>9.977370705036414</v>
+        <v>1.621322739568417</v>
       </c>
       <c r="F15" t="n">
-        <v>9.945514098582851</v>
+        <v>1.616146041019713</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>42.51471488523861</v>
+        <v>6.908641168851275</v>
       </c>
       <c r="D16" t="n">
-        <v>42.56275662709542</v>
+        <v>6.916447951903007</v>
       </c>
       <c r="E16" t="n">
-        <v>9.977370705036414</v>
+        <v>1.621322739568417</v>
       </c>
       <c r="F16" t="n">
-        <v>9.945514098582851</v>
+        <v>1.616146041019713</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>35.80861686358837</v>
+        <v>5.81890024033311</v>
       </c>
       <c r="D17" t="n">
-        <v>36.52745799433657</v>
+        <v>5.935711924079692</v>
       </c>
       <c r="E17" t="n">
-        <v>9.977370705036414</v>
+        <v>1.621322739568417</v>
       </c>
       <c r="F17" t="n">
-        <v>9.945514098582851</v>
+        <v>1.616146041019713</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>35.75656896058121</v>
+        <v>5.810442456094446</v>
       </c>
       <c r="D18" t="n">
-        <v>36.51396592335633</v>
+        <v>5.933519462545404</v>
       </c>
       <c r="E18" t="n">
-        <v>9.977370705036414</v>
+        <v>1.621322739568417</v>
       </c>
       <c r="F18" t="n">
-        <v>9.945514098582851</v>
+        <v>1.616146041019713</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>40.46975878075904</v>
+        <v>6.576335801873344</v>
       </c>
       <c r="D19" t="n">
-        <v>41.05026050346248</v>
+        <v>6.670667331812653</v>
       </c>
       <c r="E19" t="n">
-        <v>9.977370705036414</v>
+        <v>1.621322739568417</v>
       </c>
       <c r="F19" t="n">
-        <v>9.945514098582851</v>
+        <v>1.616146041019713</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
